--- a/03_EU-AI-Act_Arbeitshilfe.xlsx
+++ b/03_EU-AI-Act_Arbeitshilfe.xlsx
@@ -143,7 +143,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Rechtsstand, gegen den geprüft wurde - z. B. "29.07.2026 / Fassung 1.1". Macht nachvollziehbar, ob eine Prüfung nach einer Rechtsänderung zu wiederholen ist.</t>
+          <t xml:space="preserve">Rechtsstand, gegen den geprüft wurde - z. B. "29.07.2026 / Fassung 1.2". Macht nachvollziehbar, ob eine Prüfung nach einer Rechtsänderung zu wiederholen ist.</t>
         </r>
       </text>
     </comment>
@@ -174,12 +174,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1049" uniqueCount="639">
   <si>
     <t xml:space="preserve">EU AI Act — Arbeitshilfe zur Umsetzung</t>
   </si>
   <si>
-    <t xml:space="preserve">Fassung 1.1 · Rechtsstand: 29.07.2026 · Verordnung (EU) 2024/1689 in der Fassung der Verordnung (EU) 2026/1744 (Digital Omnibus, in Kraft seit 27.07.2026)</t>
+    <t xml:space="preserve">Fassung 1.2 · Rechtsstand: 29.07.2026 · Verordnung (EU) 2024/1689 in der Fassung der Verordnung (EU) 2026/1744 (Digital Omnibus, in Kraft seit 27.07.2026)</t>
   </si>
   <si>
     <t xml:space="preserve">Wichtiger Hinweis</t>
@@ -291,6 +291,27 @@
   </si>
   <si>
     <t xml:space="preserve">Ausgefüllter Musterfall zum Nachvollziehen — reiner Text, ohne Formeln, ohne Auswirkung auf das Dashboard.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Was noch nicht feststeht</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ausstehende Rechtsakte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diese Arbeitshilfe bildet den Rechtsstand ab. Mehrere Punkte stehen noch aus und können den Pflichtenumfang verändern: delegierte Rechtsakte nach Art. 2 Abs. 13 n. F. (bis 02.08.2027), Anhang III der Maschinenverordnung (gilt ab 02.08.2028), Leitlinien nach Art. 6 Abs. 5, Art. 96 Abs. 1 lit. g (bis 01.08.2027) und Art. 72 Abs. 3 (bis 02.09.2027) sowie mehrere Muster.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jährlicher Abgleich</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Kommission prüft nach Art. 112 Abs. 1 JEDES JAHR, ob Anhang III und die Liste der verbotenen Praktiken zu ändern sind. Gleichen Sie Ihr Inventar deshalb jährlich gegen den dann geltenden Anhang III ab — nicht nur, wenn sich an Ihren Systemen etwas ändert.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zweite Hälfte des Digital Omnibus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Digital-Omnibus-Verordnung zu Daten (COM(2025) 837, DSGVO, Data Act, ePrivacy, NIS-2) ist noch NICHT in Kraft; der Rat hat am 29.07.2026 keine Position. Sie enthält Vorschläge, die KI-Projekte unmittelbar berühren — u. a. berechtigtes Interesse für KI-Training und den Umgang mit beiläufigen sensiblen Daten. Details, Fristen und eine Beobachtungsliste im Begleitdokument „Geplante Änderungen — Digitaler Omnibus“. Nicht auf Vorschläge planen: Bis zur Veröffentlichung im Amtsblatt gilt das bestehende Recht vollständig.</t>
   </si>
   <si>
     <t xml:space="preserve">Anhang I: Abschnitt A oder Abschnitt B?</t>
@@ -1495,7 +1516,7 @@
     <t xml:space="preserve">06 — Dashboard</t>
   </si>
   <si>
-    <t xml:space="preserve">Automatische Auswertung der Blätter 01, 03, 04 und 05. Rechtsstand 29.07.2026, Fassung 1.1. Im Auslieferungszustand stehen alle Kennzahlen auf 0 — die produktiven Blätter enthalten keine Beispieldaten. Ein ausgefülltes Beispiel steht auf Blatt 09_Beispiel und wird hier nicht mitgezählt.</t>
+    <t xml:space="preserve">Automatische Auswertung der Blätter 01, 03, 04 und 05. Rechtsstand 29.07.2026, Fassung 1.2. Im Auslieferungszustand stehen alle Kennzahlen auf 0 — die produktiven Blätter enthalten keine Beispieldaten. Ein ausgefülltes Beispiel steht auf Blatt 09_Beispiel und wird hier nicht mitgezählt.</t>
   </si>
   <si>
     <t xml:space="preserve">KI-Systeme</t>
@@ -1736,6 +1757,30 @@
   </si>
   <si>
     <t xml:space="preserve">Vergleichsgrundlage: mehrere Vorschläge wurden nicht übernommen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digital-Omnibus-Verordnung (Daten) — NOCH NICHT IN KRAFT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COM(2025) 837 final vom 19.11.2025, Verfahren 2025/0360(COD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://eur-lex.europa.eu/legal-content/DE/TXT/?uri=CELEX:52025PC0837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vorschlag zur Änderung von DSGVO, Datenverordnung, ePrivacy-RL und NIS-2. Rat ohne Position (Stand 29.07.2026). NICHT als geltendes Recht behandeln — siehe Dokument „Geplante Änderungen — Digitaler Omnibus“</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stellungnahme der Datenschutzaufsicht zum Daten-Omnibus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDSA/EDSB, Gemeinsame Stellungnahme 2/2026 vom 11.02.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.edpb.europa.eu/our-work-tools/our-documents/edpbedps-joint-opinion/edpb-edps-joint-opinion-22026-proposal_en</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rät ausdrücklich von der vorgeschlagenen Neudefinition personenbezogener Daten ab</t>
   </si>
   <si>
     <t xml:space="preserve">KMU-Definition</t>
@@ -2735,7 +2780,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -2933,7 +2978,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="4" t="s">
         <v>44</v>
       </c>
@@ -2947,7 +2992,7 @@
       </c>
       <c r="C33" s="3"/>
     </row>
-    <row r="34" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="4" t="s">
         <v>47</v>
       </c>
@@ -2955,7 +3000,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="4" t="s">
         <v>49</v>
       </c>
@@ -2963,7 +3008,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="4" t="s">
         <v>51</v>
       </c>
@@ -2971,94 +3016,124 @@
         <v>52</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="4" t="s">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C38" s="3"/>
+    </row>
+    <row r="39" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B39" s="4" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="38" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="4" t="s">
+      <c r="C39" s="5" t="s">
         <v>55</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B42" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C42" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C41" s="5" t="s">
+    </row>
+    <row r="43" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B43" s="4" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="42" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="4" t="s">
+      <c r="C43" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C42" s="5" t="s">
+    </row>
+    <row r="44" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B44" s="4" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="6" t="s">
+      <c r="C44" s="5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C45" s="7"/>
-    </row>
-    <row r="46" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C46" s="8" t="s">
+      <c r="C45" s="5" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B46" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C47" s="7"/>
-    </row>
-    <row r="48" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C48" s="8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C49" s="7"/>
+      <c r="C47" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="6" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C50" s="8" t="s">
-        <v>71</v>
+      <c r="B50" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C50" s="7"/>
+    </row>
+    <row r="51" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C51" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B52" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C52" s="7"/>
+    </row>
+    <row r="53" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C53" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B54" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C54" s="7"/>
+    </row>
+    <row r="55" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C55" s="8" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="B5:C5"/>
@@ -3066,17 +3141,18 @@
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B38:C38"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation allowBlank="true" error="Bitte einen Wert aus der Liste wählen. Freitext führt zu falschen Einstufungen." errorStyle="stop" errorTitle="Ungültige Eingabe" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C45" type="list">
+    <dataValidation allowBlank="true" error="Bitte einen Wert aus der Liste wählen. Freitext führt zu falschen Einstufungen." errorStyle="stop" errorTitle="Ungültige Eingabe" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C50" type="list">
       <formula1>'08_Register'!$H$5:$H$8</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Bitte einen Wert aus der Liste wählen. Freitext führt zu falschen Einstufungen." errorStyle="stop" errorTitle="Ungültige Eingabe" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C47" type="list">
+    <dataValidation allowBlank="true" error="Bitte einen Wert aus der Liste wählen. Freitext führt zu falschen Einstufungen." errorStyle="stop" errorTitle="Ungültige Eingabe" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C52" type="list">
       <formula1>'08_Register'!$A$5:$A$7</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Bitte einen Wert aus der Liste wählen. Freitext führt zu falschen Einstufungen." errorStyle="stop" errorTitle="Ungültige Eingabe" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C49" type="list">
+    <dataValidation allowBlank="true" error="Bitte einen Wert aus der Liste wählen. Freitext führt zu falschen Einstufungen." errorStyle="stop" errorTitle="Ungültige Eingabe" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C54" type="list">
       <formula1>'08_Register'!$A$5:$A$7</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -3104,7 +3180,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>574</v>
+        <v>589</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3118,7 +3194,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>575</v>
+        <v>590</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3132,240 +3208,240 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>576</v>
+        <v>591</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>577</v>
+        <v>592</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>578</v>
+        <v>593</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>579</v>
+        <v>594</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>580</v>
+        <v>595</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>581</v>
+        <v>596</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>582</v>
+        <v>597</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>583</v>
+        <v>598</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>584</v>
+        <v>599</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>585</v>
+        <v>600</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>586</v>
+        <v>601</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>586</v>
+        <v>601</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>587</v>
+        <v>602</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>588</v>
+        <v>603</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>589</v>
+        <v>604</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>584</v>
+        <v>599</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>590</v>
+        <v>605</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>584</v>
+        <v>599</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>591</v>
+        <v>606</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>592</v>
+        <v>607</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>593</v>
+        <v>608</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>594</v>
+        <v>609</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>595</v>
+        <v>610</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>596</v>
+        <v>611</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>597</v>
+        <v>612</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>591</v>
+        <v>606</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>591</v>
+        <v>606</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>598</v>
+        <v>613</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>599</v>
+        <v>614</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="E7" s="5" t="s">
+        <v>615</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>617</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>618</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>619</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>620</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="L7" s="5" t="s">
         <v>600</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>601</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>602</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>603</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>604</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>605</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>608</v>
+        <v>623</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>609</v>
+        <v>624</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>610</v>
+        <v>625</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>611</v>
+        <v>626</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>612</v>
+        <v>627</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>605</v>
+        <v>620</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C9" s="5" t="s">
-        <v>613</v>
+        <v>628</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>614</v>
+        <v>629</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>615</v>
+        <v>630</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>616</v>
+        <v>631</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C10" s="5" t="s">
-        <v>605</v>
+        <v>620</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>617</v>
+        <v>632</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>618</v>
+        <v>633</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D11" s="5" t="s">
-        <v>619</v>
+        <v>634</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>620</v>
+        <v>635</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D12" s="5" t="s">
-        <v>621</v>
+        <v>636</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>622</v>
+        <v>637</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D13" s="5" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>623</v>
+        <v>638</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D14" s="5" t="s">
-        <v>605</v>
+        <v>620</v>
       </c>
     </row>
   </sheetData>
@@ -3406,7 +3482,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3421,7 +3497,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3436,37 +3512,37 @@
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4476,7 +4552,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4491,7 +4567,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4506,40 +4582,40 @@
     </row>
     <row r="5" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6004,7 +6080,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6028,7 +6104,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -6052,64 +6128,64 @@
     </row>
     <row r="5" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="G5" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="P5" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q5" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="R5" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="S5" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="H5" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="L5" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="M5" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="N5" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="O5" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="P5" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q5" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="R5" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="S5" s="9" t="s">
-        <v>97</v>
-      </c>
       <c r="T5" s="9" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8623,7 +8699,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -8641,7 +8717,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -8659,69 +8735,69 @@
     </row>
     <row r="5" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="M5" s="9" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="N5" s="9" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
@@ -8736,25 +8812,25 @@
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
@@ -8769,25 +8845,25 @@
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C8" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="D8" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="D8" s="13" t="s">
-        <v>135</v>
-      </c>
       <c r="E8" s="13" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
@@ -8802,25 +8878,25 @@
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="E9" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="F9" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="G9" s="13" t="s">
         <v>145</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="G9" s="13" t="s">
-        <v>138</v>
       </c>
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
@@ -8835,25 +8911,25 @@
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="B10" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="G10" s="13" t="s">
         <v>145</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>138</v>
       </c>
       <c r="H10" s="7"/>
       <c r="I10" s="7"/>
@@ -8868,25 +8944,25 @@
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="B11" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="G11" s="13" t="s">
         <v>145</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>138</v>
       </c>
       <c r="H11" s="7"/>
       <c r="I11" s="7"/>
@@ -8901,25 +8977,25 @@
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="B12" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="G12" s="13" t="s">
         <v>145</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>138</v>
       </c>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
@@ -8934,25 +9010,25 @@
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B13" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="G13" s="13" t="s">
         <v>145</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>138</v>
       </c>
       <c r="H13" s="7"/>
       <c r="I13" s="7"/>
@@ -8967,25 +9043,25 @@
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B14" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="G14" s="13" t="s">
         <v>145</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>138</v>
       </c>
       <c r="H14" s="7"/>
       <c r="I14" s="7"/>
@@ -9000,25 +9076,25 @@
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="B15" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="G15" s="13" t="s">
         <v>145</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>138</v>
       </c>
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
@@ -9033,25 +9109,25 @@
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="B16" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="G16" s="13" t="s">
         <v>145</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>138</v>
       </c>
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
@@ -9066,25 +9142,25 @@
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="H17" s="7"/>
       <c r="I17" s="7"/>
@@ -9099,25 +9175,25 @@
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="7"/>
@@ -9132,25 +9208,25 @@
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="7"/>
@@ -9165,25 +9241,25 @@
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
@@ -9198,25 +9274,25 @@
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="D21" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="E21" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="E21" s="13" t="s">
-        <v>178</v>
-      </c>
       <c r="F21" s="13" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
@@ -9231,25 +9307,25 @@
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
@@ -9264,25 +9340,25 @@
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
@@ -9297,25 +9373,25 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="H24" s="7"/>
       <c r="I24" s="7"/>
@@ -9330,25 +9406,25 @@
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
@@ -9363,25 +9439,25 @@
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
@@ -9396,25 +9472,25 @@
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
@@ -9429,25 +9505,25 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
@@ -9462,25 +9538,25 @@
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
@@ -9495,25 +9571,25 @@
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
@@ -9528,25 +9604,25 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
@@ -9561,25 +9637,25 @@
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
@@ -9594,25 +9670,25 @@
     </row>
     <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
@@ -9627,25 +9703,25 @@
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="H34" s="7"/>
       <c r="I34" s="7"/>
@@ -9660,25 +9736,25 @@
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="C35" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="F35" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="D35" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="E35" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="F35" s="13" t="s">
-        <v>226</v>
-      </c>
       <c r="G35" s="13" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="H35" s="7"/>
       <c r="I35" s="7"/>
@@ -9693,25 +9769,25 @@
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="H36" s="7"/>
       <c r="I36" s="7"/>
@@ -9726,25 +9802,25 @@
     </row>
     <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="B37" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="B37" s="13" t="s">
-        <v>232</v>
-      </c>
       <c r="C37" s="13" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="H37" s="7"/>
       <c r="I37" s="7"/>
@@ -9759,25 +9835,25 @@
     </row>
     <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="H38" s="7"/>
       <c r="I38" s="7"/>
@@ -9792,25 +9868,25 @@
     </row>
     <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="13" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H39" s="7"/>
       <c r="I39" s="7"/>
@@ -9825,25 +9901,25 @@
     </row>
     <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="13" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H40" s="7"/>
       <c r="I40" s="7"/>
@@ -9858,25 +9934,25 @@
     </row>
     <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="13" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G41" s="13" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H41" s="7"/>
       <c r="I41" s="7"/>
@@ -9891,25 +9967,25 @@
     </row>
     <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="13" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H42" s="7"/>
       <c r="I42" s="7"/>
@@ -9924,25 +10000,25 @@
     </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H43" s="7"/>
       <c r="I43" s="7"/>
@@ -9957,25 +10033,25 @@
     </row>
     <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="13" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H44" s="7"/>
       <c r="I44" s="7"/>
@@ -9990,25 +10066,25 @@
     </row>
     <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="13" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H45" s="7"/>
       <c r="I45" s="7"/>
@@ -10023,25 +10099,25 @@
     </row>
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="13" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G46" s="13" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H46" s="7"/>
       <c r="I46" s="7"/>
@@ -10056,25 +10132,25 @@
     </row>
     <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="13" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H47" s="7"/>
       <c r="I47" s="7"/>
@@ -10089,25 +10165,25 @@
     </row>
     <row r="48" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="13" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G48" s="13" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H48" s="7"/>
       <c r="I48" s="7"/>
@@ -10122,25 +10198,25 @@
     </row>
     <row r="49" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="13" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="D49" s="13" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H49" s="7"/>
       <c r="I49" s="7"/>
@@ -10155,25 +10231,25 @@
     </row>
     <row r="50" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="13" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="D50" s="13" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F50" s="13" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="H50" s="7"/>
       <c r="I50" s="7"/>
@@ -10188,25 +10264,25 @@
     </row>
     <row r="51" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="13" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F51" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G51" s="13" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H51" s="7"/>
       <c r="I51" s="7"/>
@@ -10221,25 +10297,25 @@
     </row>
     <row r="52" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="13" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="D52" s="13" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F52" s="13" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="G52" s="13" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="H52" s="7"/>
       <c r="I52" s="7"/>
@@ -10254,25 +10330,25 @@
     </row>
     <row r="53" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="13" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F53" s="13" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="G53" s="13" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="H53" s="7"/>
       <c r="I53" s="7"/>
@@ -10287,25 +10363,25 @@
     </row>
     <row r="54" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="13" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="D54" s="13" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="G54" s="13" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="H54" s="7"/>
       <c r="I54" s="7"/>
@@ -10320,25 +10396,25 @@
     </row>
     <row r="55" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="13" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="G55" s="13" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="H55" s="7"/>
       <c r="I55" s="7"/>
@@ -10353,25 +10429,25 @@
     </row>
     <row r="56" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="B56" s="13" t="s">
         <v>301</v>
       </c>
-      <c r="B56" s="13" t="s">
-        <v>294</v>
-      </c>
       <c r="C56" s="13" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="G56" s="13" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="H56" s="7"/>
       <c r="I56" s="7"/>
@@ -10386,25 +10462,25 @@
     </row>
     <row r="57" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="13" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="D57" s="13" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="G57" s="13" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="H57" s="7"/>
       <c r="I57" s="7"/>
@@ -10419,25 +10495,25 @@
     </row>
     <row r="58" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="13" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G58" s="13" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H58" s="7"/>
       <c r="I58" s="7"/>
@@ -10452,25 +10528,25 @@
     </row>
     <row r="59" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="13" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G59" s="13" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H59" s="7"/>
       <c r="I59" s="7"/>
@@ -10485,25 +10561,25 @@
     </row>
     <row r="60" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="13" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="D60" s="13" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F60" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G60" s="13" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H60" s="7"/>
       <c r="I60" s="7"/>
@@ -10518,25 +10594,25 @@
     </row>
     <row r="61" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="13" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="D61" s="13" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G61" s="13" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H61" s="7"/>
       <c r="I61" s="7"/>
@@ -10551,25 +10627,25 @@
     </row>
     <row r="62" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="13" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="D62" s="13" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G62" s="13" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H62" s="7"/>
       <c r="I62" s="7"/>
@@ -10584,25 +10660,25 @@
     </row>
     <row r="63" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="13" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="D63" s="13" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F63" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G63" s="13" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H63" s="7"/>
       <c r="I63" s="7"/>
@@ -10617,25 +10693,25 @@
     </row>
     <row r="64" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="13" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="D64" s="13" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F64" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G64" s="13" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H64" s="7"/>
       <c r="I64" s="7"/>
@@ -10650,25 +10726,25 @@
     </row>
     <row r="65" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="13" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F65" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G65" s="13" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H65" s="7"/>
       <c r="I65" s="7"/>
@@ -10683,25 +10759,25 @@
     </row>
     <row r="66" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="13" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F66" s="13" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="G66" s="13" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="H66" s="7"/>
       <c r="I66" s="7"/>
@@ -10716,25 +10792,25 @@
     </row>
     <row r="67" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="13" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="D67" s="13" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F67" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G67" s="13" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H67" s="7"/>
       <c r="I67" s="7"/>
@@ -10749,25 +10825,25 @@
     </row>
     <row r="68" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="13" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F68" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G68" s="13" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H68" s="7"/>
       <c r="I68" s="7"/>
@@ -10782,25 +10858,25 @@
     </row>
     <row r="69" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="13" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="D69" s="13" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F69" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G69" s="13" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H69" s="7"/>
       <c r="I69" s="7"/>
@@ -10815,25 +10891,25 @@
     </row>
     <row r="70" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="13" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="B70" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="D70" s="13" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F70" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G70" s="13" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H70" s="7"/>
       <c r="I70" s="7"/>
@@ -10848,25 +10924,25 @@
     </row>
     <row r="71" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="13" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="D71" s="13" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F71" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G71" s="13" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H71" s="7"/>
       <c r="I71" s="7"/>
@@ -10881,25 +10957,25 @@
     </row>
     <row r="72" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="13" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="D72" s="13" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="E72" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F72" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G72" s="13" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H72" s="7"/>
       <c r="I72" s="7"/>
@@ -10914,25 +10990,25 @@
     </row>
     <row r="73" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="13" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="B73" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="D73" s="13" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="E73" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F73" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G73" s="13" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H73" s="7"/>
       <c r="I73" s="7"/>
@@ -10947,25 +11023,25 @@
     </row>
     <row r="74" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="13" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="D74" s="13" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="E74" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F74" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G74" s="13" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H74" s="7"/>
       <c r="I74" s="7"/>
@@ -10980,25 +11056,25 @@
     </row>
     <row r="75" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="13" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="B75" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C75" s="13" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="D75" s="13" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F75" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G75" s="13" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H75" s="7"/>
       <c r="I75" s="7"/>
@@ -11013,25 +11089,25 @@
     </row>
     <row r="76" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="13" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C76" s="13" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="D76" s="13" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="E76" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F76" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G76" s="13" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="H76" s="7"/>
       <c r="I76" s="7"/>
@@ -11046,25 +11122,25 @@
     </row>
     <row r="77" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="13" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="B77" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C77" s="13" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F77" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G77" s="13" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H77" s="7"/>
       <c r="I77" s="7"/>
@@ -11079,25 +11155,25 @@
     </row>
     <row r="78" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="13" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="B78" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C78" s="13" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="D78" s="13" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F78" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G78" s="13" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H78" s="7"/>
       <c r="I78" s="7"/>
@@ -11112,25 +11188,25 @@
     </row>
     <row r="79" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="13" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="B79" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C79" s="13" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="D79" s="13" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F79" s="13" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="G79" s="13" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="H79" s="7"/>
       <c r="I79" s="7"/>
@@ -11145,25 +11221,25 @@
     </row>
     <row r="80" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="13" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B80" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C80" s="13" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="D80" s="13" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F80" s="13" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="G80" s="13" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="H80" s="7"/>
       <c r="I80" s="7"/>
@@ -11178,25 +11254,25 @@
     </row>
     <row r="81" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="13" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="B81" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C81" s="13" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="D81" s="13" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F81" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G81" s="13" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H81" s="7"/>
       <c r="I81" s="7"/>
@@ -11211,25 +11287,25 @@
     </row>
     <row r="82" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="13" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="B82" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C82" s="13" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="D82" s="13" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F82" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G82" s="13" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H82" s="7"/>
       <c r="I82" s="7"/>
@@ -11244,25 +11320,25 @@
     </row>
     <row r="83" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="13" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="B83" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C83" s="13" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="D83" s="13" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="E83" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F83" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G83" s="13" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H83" s="7"/>
       <c r="I83" s="7"/>
@@ -11277,25 +11353,25 @@
     </row>
     <row r="84" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="13" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="B84" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C84" s="13" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="D84" s="13" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F84" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G84" s="13" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H84" s="7"/>
       <c r="I84" s="7"/>
@@ -11310,25 +11386,25 @@
     </row>
     <row r="85" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="13" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="B85" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C85" s="13" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="D85" s="13" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="E85" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F85" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G85" s="13" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H85" s="7"/>
       <c r="I85" s="7"/>
@@ -11343,25 +11419,25 @@
     </row>
     <row r="86" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="13" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="B86" s="13" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="C86" s="13" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="D86" s="13" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="E86" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F86" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G86" s="13" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="H86" s="7"/>
       <c r="I86" s="7"/>
@@ -11376,25 +11452,25 @@
     </row>
     <row r="87" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="13" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="B87" s="13" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="C87" s="13" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="D87" s="13" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="E87" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F87" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G87" s="13" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="H87" s="7"/>
       <c r="I87" s="7"/>
@@ -11409,25 +11485,25 @@
     </row>
     <row r="88" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="13" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="B88" s="13" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="C88" s="13" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="D88" s="13" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="E88" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F88" s="13" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G88" s="13" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="H88" s="7"/>
       <c r="I88" s="7"/>
@@ -11442,25 +11518,25 @@
     </row>
     <row r="89" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="13" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="B89" s="13" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="C89" s="13" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="D89" s="13" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F89" s="13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G89" s="13" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="H89" s="7"/>
       <c r="I89" s="7"/>
@@ -11475,25 +11551,25 @@
     </row>
     <row r="90" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="13" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="B90" s="13" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="C90" s="13" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="D90" s="13" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="E90" s="13" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="F90" s="13" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G90" s="13" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="H90" s="7"/>
       <c r="I90" s="7"/>
@@ -11508,25 +11584,25 @@
     </row>
     <row r="91" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="13" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="B91" s="13" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="C91" s="13" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="D91" s="13" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F91" s="13" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="G91" s="13" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="H91" s="7"/>
       <c r="I91" s="7"/>
@@ -11541,25 +11617,25 @@
     </row>
     <row r="92" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="13" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="B92" s="13" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="C92" s="13" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="D92" s="13" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="E92" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F92" s="13" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="G92" s="13" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="H92" s="7"/>
       <c r="I92" s="7"/>
@@ -11574,25 +11650,25 @@
     </row>
     <row r="93" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="13" t="s">
+        <v>422</v>
+      </c>
+      <c r="B93" s="13" t="s">
         <v>415</v>
       </c>
-      <c r="B93" s="13" t="s">
-        <v>408</v>
-      </c>
       <c r="C93" s="13" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D93" s="13" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="E93" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F93" s="13" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="G93" s="13" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="H93" s="7"/>
       <c r="I93" s="7"/>
@@ -11607,25 +11683,25 @@
     </row>
     <row r="94" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="13" t="s">
+        <v>425</v>
+      </c>
+      <c r="B94" s="13" t="s">
+        <v>415</v>
+      </c>
+      <c r="C94" s="13" t="s">
+        <v>426</v>
+      </c>
+      <c r="D94" s="13" t="s">
+        <v>427</v>
+      </c>
+      <c r="E94" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="F94" s="13" t="s">
+        <v>415</v>
+      </c>
+      <c r="G94" s="13" t="s">
         <v>418</v>
-      </c>
-      <c r="B94" s="13" t="s">
-        <v>408</v>
-      </c>
-      <c r="C94" s="13" t="s">
-        <v>419</v>
-      </c>
-      <c r="D94" s="13" t="s">
-        <v>420</v>
-      </c>
-      <c r="E94" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="F94" s="13" t="s">
-        <v>408</v>
-      </c>
-      <c r="G94" s="13" t="s">
-        <v>411</v>
       </c>
       <c r="H94" s="7"/>
       <c r="I94" s="7"/>
@@ -11640,25 +11716,25 @@
     </row>
     <row r="95" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="13" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="B95" s="13" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="C95" s="13" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="D95" s="13" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="E95" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F95" s="13" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="G95" s="13" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="H95" s="7"/>
       <c r="I95" s="7"/>
@@ -11673,7 +11749,7 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="15" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="B97" s="15"/>
       <c r="C97" s="15"/>
@@ -11751,7 +11827,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -11766,7 +11842,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -11781,37 +11857,37 @@
     </row>
     <row r="5" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12951,7 +13027,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -12959,7 +13035,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -12967,23 +13043,23 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="6" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="9" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="C7" s="17" t="n">
         <f aca="false">COUNTIF('01_KI-Inventar'!$B$6:$B$65,"?*")</f>
@@ -12993,7 +13069,7 @@
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="C8" s="17" t="n">
         <f aca="false">COUNTIF('03_Risiko-Einstufung'!$K$6:$K$65,"?*")</f>
@@ -13003,131 +13079,131 @@
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="C9" s="17" t="n">
         <f aca="false">COUNTIF('03_Risiko-Einstufung'!$K$6:$K$65,"VERBOTEN (Art. 5)")</f>
         <v>0</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="C10" s="17" t="n">
         <f aca="false">COUNTIF('03_Risiko-Einstufung'!$K$6:$K$65,"Hochrisiko Anhang III")</f>
         <v>0</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="C11" s="17" t="n">
         <f aca="false">COUNTIF('03_Risiko-Einstufung'!$K$6:$K$65,"Hochrisiko Anhang I Abschnitt A")</f>
         <v>0</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="C12" s="17" t="n">
         <f aca="false">COUNTIF('03_Risiko-Einstufung'!$K$6:$K$65,"Hochrisiko Anhang I Abschnitt A und Anhang III")</f>
         <v>0</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="C13" s="17" t="n">
         <f aca="false">COUNTIF('03_Risiko-Einstufung'!$K$6:$K$65,"Hochrisiko Anhang I Abschnitt B*")</f>
         <v>0</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="C14" s="17" t="n">
         <f aca="false">COUNTIF('03_Risiko-Einstufung'!$K$6:$K$65,"Kein Hochrisiko (Art. 6 Abs. 3)")</f>
         <v>0</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="5" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="C15" s="17" t="n">
         <f aca="false">COUNTIF('03_Risiko-Einstufung'!$K$6:$K$65,"Transparenzpflicht (Art. 50)")</f>
         <v>0</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="5" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="C16" s="17" t="n">
         <f aca="false">COUNTIF('03_Risiko-Einstufung'!$K$6:$K$65,"Geringes Risiko")</f>
         <v>0</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="5" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="C17" s="17" t="n">
         <f aca="false">COUNTIF('03_Risiko-Einstufung'!$K$6:$K$65,"noch offen*")</f>
         <v>0</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="6" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="9" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="5" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="C21" s="17" t="n">
         <f aca="false">COUNTIF('03_Risiko-Einstufung'!$P$6:$P$65,"Einstufung bestätigt")</f>
@@ -13137,71 +13213,71 @@
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="C22" s="17" t="n">
         <f aca="false">COUNTIF('03_Risiko-Einstufung'!$P$6:$P$65,"Arbeitsannahme — nicht bestätigt")</f>
         <v>0</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="5" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="C23" s="17" t="n">
         <f aca="false">COUNTIF('03_Risiko-Einstufung'!$P$6:$P$65,"Juristische Prüfung erforderlich")</f>
         <v>0</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="5" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="C24" s="17" t="n">
         <f aca="false">COUNTIF('03_Risiko-Einstufung'!$P$6:$P$65,"Prüfung unvollständig")</f>
         <v>0</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="5" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="C25" s="17" t="n">
         <f aca="false">COUNTIFS('03_Risiko-Einstufung'!$K$6:$K$65,"?*",'03_Risiko-Einstufung'!$R$6:$R$65,"")</f>
         <v>0</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="6" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="9" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="5" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="C29" s="17" t="n">
         <f aca="false">COUNTIF('04_Pflichten-Matrix'!$H$6:$H$95,"Ja")</f>
@@ -13211,7 +13287,7 @@
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="5" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="C30" s="17" t="n">
         <f aca="false">COUNTIFS('04_Pflichten-Matrix'!$H$6:$H$95,"Ja",'04_Pflichten-Matrix'!$I$6:$I$95,"erfüllt")</f>
@@ -13221,7 +13297,7 @@
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="5" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="C31" s="17" t="n">
         <f aca="false">COUNTIFS('04_Pflichten-Matrix'!$H$6:$H$95,"Ja",'04_Pflichten-Matrix'!$I$6:$I$95,"in Arbeit")</f>
@@ -13231,7 +13307,7 @@
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="5" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="C32" s="17" t="n">
         <f aca="false">COUNTIFS('04_Pflichten-Matrix'!$H$6:$H$95,"Ja",'04_Pflichten-Matrix'!$I$6:$I$95,"offen")</f>
@@ -13241,59 +13317,59 @@
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="5" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="C33" s="17" t="n">
         <f aca="false">COUNTIFS('04_Pflichten-Matrix'!$H$6:$H$95,"Ja",'04_Pflichten-Matrix'!$I$6:$I$95,"")</f>
         <v>0</v>
       </c>
       <c r="D33" s="18" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="5" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="C34" s="19" t="n">
         <f aca="false">IFERROR(COUNTIFS('04_Pflichten-Matrix'!$H$6:$H$95,"Ja",'04_Pflichten-Matrix'!$I$6:$I$95,"erfüllt")/(COUNTIF('04_Pflichten-Matrix'!$H$6:$H$95,"Ja")-COUNTIFS('04_Pflichten-Matrix'!$H$6:$H$95,"Ja",'04_Pflichten-Matrix'!$I$6:$I$95,"nicht anwendbar")),0)</f>
         <v>0</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="5" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="C35" s="17" t="n">
         <f aca="false">COUNTIF('04_Pflichten-Matrix'!$H$6:$H$95,"noch offen")+COUNTIF('04_Pflichten-Matrix'!$H$6:$H$95,"")</f>
         <v>90</v>
       </c>
       <c r="D35" s="18" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="6" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="9" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="5" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="C39" s="17" t="n">
         <f aca="false">COUNTIF('05_Maßnahmenplan'!$E$6:$E$65,"?*")</f>
@@ -13303,31 +13379,31 @@
     </row>
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="5" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="C40" s="17" t="n">
         <f aca="false">COUNTIFS('05_Maßnahmenplan'!$E$6:$E$65,"?*",'05_Maßnahmenplan'!$G$6:$G$65,"")</f>
         <v>0</v>
       </c>
       <c r="D40" s="18" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="5" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="C41" s="17" t="n">
         <f aca="false">COUNTIF('05_Maßnahmenplan'!$J$6:$J$65,"überfällig")</f>
         <v>0</v>
       </c>
       <c r="D41" s="18" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="5" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="C42" s="17" t="n">
         <f aca="false">COUNTIF('05_Maßnahmenplan'!$J$6:$J$65,"fällig in 30 Tagen")</f>
@@ -13337,7 +13413,7 @@
     </row>
     <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="5" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="C43" s="17" t="n">
         <f aca="false">COUNTIF('05_Maßnahmenplan'!$J$6:$J$65,"abgeschlossen")</f>
@@ -13347,23 +13423,23 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="6" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="9" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="5" t="s">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="C47" s="20" t="n">
         <f aca="false">DATE(2026,8,2)</f>
@@ -13373,7 +13449,7 @@
     </row>
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="5" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="C48" s="20" t="n">
         <f aca="false">DATE(2026,12,2)</f>
@@ -13383,7 +13459,7 @@
     </row>
     <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="5" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="C49" s="20" t="n">
         <f aca="false">DATE(2027,12,2)</f>
@@ -13393,7 +13469,7 @@
     </row>
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="5" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="C50" s="20" t="n">
         <f aca="false">DATE(2028,8,2)</f>
@@ -13403,19 +13479,19 @@
     </row>
     <row r="51" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="5" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="C51" s="20" t="n">
         <f aca="false">DATE(2027,8,2)</f>
         <v>46601</v>
       </c>
       <c r="D51" s="18" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="15" t="s">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="C53" s="15"/>
       <c r="D53" s="15"/>
@@ -13441,7 +13517,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="40"/>
@@ -13453,7 +13529,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -13461,7 +13537,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -13469,250 +13545,270 @@
     </row>
     <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>520</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>522</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>513</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="F8" s="5" t="s">
         <v>514</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>515</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>506</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>530</v>
-      </c>
-      <c r="D12" s="5"/>
+        <v>537</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>538</v>
+      </c>
       <c r="E12" s="5" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>531</v>
+        <v>514</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>531</v>
+        <v>514</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>538</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>539</v>
-      </c>
+        <v>545</v>
+      </c>
+      <c r="D14" s="5"/>
       <c r="E14" s="5" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="22" t="s">
-        <v>547</v>
-      </c>
-      <c r="B19" s="22"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-    </row>
-    <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="22" t="s">
-        <v>548</v>
-      </c>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
+    <row r="16" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>551</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>552</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>553</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>513</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
+        <v>556</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>557</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>558</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>559</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>513</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
+        <v>561</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="22" t="s">
-        <v>549</v>
+        <v>562</v>
       </c>
       <c r="B21" s="22"/>
       <c r="C21" s="22"/>
@@ -13722,7 +13818,7 @@
     </row>
     <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="22" t="s">
-        <v>550</v>
+        <v>563</v>
       </c>
       <c r="B22" s="22"/>
       <c r="C22" s="22"/>
@@ -13732,7 +13828,7 @@
     </row>
     <row r="23" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="22" t="s">
-        <v>551</v>
+        <v>564</v>
       </c>
       <c r="B23" s="22"/>
       <c r="C23" s="22"/>
@@ -13740,27 +13836,49 @@
       <c r="E23" s="22"/>
       <c r="F23" s="22"/>
     </row>
+    <row r="24" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="22" t="s">
+        <v>565</v>
+      </c>
+      <c r="B24" s="22"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+    </row>
+    <row r="25" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="22" t="s">
+        <v>566</v>
+      </c>
+      <c r="B25" s="22"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+    </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A20:F20"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C6" r:id="rId1" display="https://eur-lex.europa.eu/eli/reg/2024/1689/oj/deu"/>
     <hyperlink ref="C7" r:id="rId2" display="https://eur-lex.europa.eu/eli/reg/2026/1744/oj/deu"/>
     <hyperlink ref="C8" r:id="rId3" display="https://eur-lex.europa.eu/legal-content/DE/TXT/?uri=CELEX:52025PC0836"/>
-    <hyperlink ref="C9" r:id="rId4" display="https://eur-lex.europa.eu/legal-content/DE/TXT/?uri=CELEX:32003H0361"/>
-    <hyperlink ref="C10" r:id="rId5" display="https://eur-lex.europa.eu/legal-content/DE/TXT/PDF/?uri=OJ:L_202501099"/>
-    <hyperlink ref="C11" r:id="rId6" display="https://eur-lex.europa.eu/legal-content/DE/TXT/?uri=CELEX:32011L0093"/>
-    <hyperlink ref="C12" r:id="rId7" display="https://www.consilium.europa.eu/en/press/press-releases/2026/06/29/artificial-intelligence-council-gives-final-green-light-to-simplify-and-streamline-rules/"/>
-    <hyperlink ref="C13" r:id="rId8" display="https://www.europarl.europa.eu/legislative-train/package-digital-package/file-digital-omnibus-on-ai"/>
-    <hyperlink ref="C14" r:id="rId9" display="https://artificialintelligenceact.eu/de/"/>
-    <hyperlink ref="C15" r:id="rId10" display="https://ai-act-law.eu/de/"/>
+    <hyperlink ref="C9" r:id="rId4" display="https://eur-lex.europa.eu/legal-content/DE/TXT/?uri=CELEX:52025PC0837"/>
+    <hyperlink ref="C10" r:id="rId5" display="https://www.edpb.europa.eu/our-work-tools/our-documents/edpbedps-joint-opinion/edpb-edps-joint-opinion-22026-proposal_en"/>
+    <hyperlink ref="C11" r:id="rId6" display="https://eur-lex.europa.eu/legal-content/DE/TXT/?uri=CELEX:32003H0361"/>
+    <hyperlink ref="C12" r:id="rId7" display="https://eur-lex.europa.eu/legal-content/DE/TXT/PDF/?uri=OJ:L_202501099"/>
+    <hyperlink ref="C13" r:id="rId8" display="https://eur-lex.europa.eu/legal-content/DE/TXT/?uri=CELEX:32011L0093"/>
+    <hyperlink ref="C14" r:id="rId9" display="https://www.consilium.europa.eu/en/press/press-releases/2026/06/29/artificial-intelligence-council-gives-final-green-light-to-simplify-and-streamline-rules/"/>
+    <hyperlink ref="C15" r:id="rId10" display="https://www.europarl.europa.eu/legislative-train/package-digital-package/file-digital-omnibus-on-ai"/>
+    <hyperlink ref="C16" r:id="rId11" display="https://artificialintelligenceact.eu/de/"/>
+    <hyperlink ref="C17" r:id="rId12" display="https://ai-act-law.eu/de/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.5"/>
@@ -13787,35 +13905,35 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>552</v>
+        <v>567</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>553</v>
+        <v>568</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="3" t="s">
-        <v>554</v>
+        <v>569</v>
       </c>
       <c r="C5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
-        <v>555</v>
+        <v>570</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>556</v>
+        <v>571</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="3" t="s">
-        <v>557</v>
+        <v>572</v>
       </c>
       <c r="C8" s="3"/>
     </row>
@@ -13824,7 +13942,7 @@
         <v>21</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>558</v>
+        <v>573</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13832,15 +13950,15 @@
         <v>23</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>559</v>
+        <v>574</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="4" t="s">
-        <v>560</v>
+        <v>575</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>561</v>
+        <v>576</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13848,23 +13966,23 @@
         <v>25</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>562</v>
+        <v>577</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="4" t="s">
-        <v>563</v>
+        <v>578</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>564</v>
+        <v>579</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="4" t="s">
-        <v>565</v>
+        <v>580</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>566</v>
+        <v>581</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13872,7 +13990,7 @@
         <v>27</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>567</v>
+        <v>582</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13880,29 +13998,29 @@
         <v>29</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>568</v>
+        <v>583</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="3" t="s">
-        <v>569</v>
+        <v>584</v>
       </c>
       <c r="C18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="4" t="s">
-        <v>570</v>
+        <v>585</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>571</v>
+        <v>586</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="4" t="s">
-        <v>572</v>
+        <v>587</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>573</v>
+        <v>588</v>
       </c>
     </row>
   </sheetData>
